--- a/data_lake/industry/CFM/uMCP.xlsx
+++ b/data_lake/industry/CFM/uMCP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10821"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\industry\CFM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/industry/CFM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{286BA6F1-B446-4152-8DEA-B8C3A19AEB5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{198C9074-920B-B847-ABF7-D05982F89C3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="666" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18020" yWindow="780" windowWidth="17980" windowHeight="20760" tabRatio="666" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="uMCP(LPDDR4X + UFS2.2)4GB+128GB" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="9">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -70,31 +70,31 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="179" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="180" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="166" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="167" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -132,55 +132,55 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
-    <cellStyle name="쉼표 [0]" xfId="2" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -458,19 +458,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G60"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="9"/>
-    <col min="7" max="7" width="11.19921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.1640625" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -493,7 +493,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -516,7 +516,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -539,7 +539,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -562,7 +562,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -585,7 +585,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -608,7 +608,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -631,7 +631,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -654,7 +654,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -677,7 +677,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -700,7 +700,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -723,7 +723,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -746,7 +746,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -769,7 +769,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -792,7 +792,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -815,7 +815,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -838,7 +838,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -861,7 +861,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -884,7 +884,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -907,7 +907,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -930,7 +930,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -953,7 +953,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -976,7 +976,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -999,7 +999,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -1022,7 +1022,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -1045,7 +1045,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -1068,7 +1068,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -1091,7 +1091,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -1114,7 +1114,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -1137,7 +1137,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -1160,7 +1160,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -1183,7 +1183,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -1206,7 +1206,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -1229,7 +1229,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -1252,7 +1252,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -1275,7 +1275,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -1298,7 +1298,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -1321,7 +1321,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -1344,7 +1344,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -1367,7 +1367,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -1390,7 +1390,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -1413,7 +1413,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -1436,7 +1436,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -1459,7 +1459,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -1482,7 +1482,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -1505,7 +1505,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -1528,7 +1528,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -1551,7 +1551,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -1574,7 +1574,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="10">
         <v>46210</v>
       </c>
@@ -1597,7 +1597,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="10">
         <v>46217</v>
       </c>
@@ -1620,7 +1620,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="10">
         <v>46224</v>
       </c>
@@ -1643,7 +1643,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="10">
         <v>46231</v>
       </c>
@@ -1666,7 +1666,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="10">
         <v>46238</v>
       </c>
@@ -1686,6 +1686,167 @@
         <v>92.2</v>
       </c>
       <c r="G53" s="9">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="B54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C54" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="9">
+        <v>89.1</v>
+      </c>
+      <c r="F54" s="9">
+        <v>92.2</v>
+      </c>
+      <c r="G54" s="9">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="B55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="C55" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="9">
+        <v>89.1</v>
+      </c>
+      <c r="F55" s="9">
+        <v>92.2</v>
+      </c>
+      <c r="G55" s="9">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="B56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="C56" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="9">
+        <v>89.1</v>
+      </c>
+      <c r="F56" s="9">
+        <v>92.2</v>
+      </c>
+      <c r="G56" s="9">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="B57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="C57" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="9">
+        <v>89.1</v>
+      </c>
+      <c r="F57" s="9">
+        <v>92.2</v>
+      </c>
+      <c r="G57" s="9">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="B58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="C58" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="9">
+        <v>89.1</v>
+      </c>
+      <c r="F58" s="9">
+        <v>92.2</v>
+      </c>
+      <c r="G58" s="9">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="B59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="C59" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="9">
+        <v>89.1</v>
+      </c>
+      <c r="F59" s="9">
+        <v>92.2</v>
+      </c>
+      <c r="G59" s="9">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="B60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="C60" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="9">
+        <v>89.1</v>
+      </c>
+      <c r="F60" s="9">
+        <v>92.2</v>
+      </c>
+      <c r="G60" s="9">
         <v>91</v>
       </c>
     </row>
@@ -1697,19 +1858,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BBFB96D-E0DC-4AFD-BE63-80A1B57B983E}">
-  <dimension ref="A1:G53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G60"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9.59765625" style="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.19921875" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9.6640625" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.1640625" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1732,7 +1893,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -1755,7 +1916,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -1778,7 +1939,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -1801,7 +1962,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -1824,7 +1985,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -1847,7 +2008,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -1870,7 +2031,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -1893,7 +2054,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -1916,7 +2077,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -1939,7 +2100,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -1962,7 +2123,7 @@
         <v>26.3</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -1985,7 +2146,7 @@
         <v>26.3</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -2008,7 +2169,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -2031,7 +2192,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -2054,7 +2215,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -2077,7 +2238,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -2100,7 +2261,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -2123,7 +2284,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -2146,7 +2307,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -2169,7 +2330,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -2192,7 +2353,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -2215,7 +2376,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -2238,7 +2399,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -2261,7 +2422,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -2284,7 +2445,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -2307,7 +2468,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -2330,7 +2491,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -2353,7 +2514,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -2376,7 +2537,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -2399,7 +2560,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -2422,7 +2583,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -2445,7 +2606,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -2468,7 +2629,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -2491,7 +2652,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -2514,7 +2675,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -2537,7 +2698,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -2560,7 +2721,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -2583,7 +2744,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -2606,7 +2767,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -2629,7 +2790,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -2652,7 +2813,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -2675,7 +2836,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -2698,7 +2859,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -2721,7 +2882,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -2744,7 +2905,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -2767,7 +2928,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -2790,7 +2951,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -2813,7 +2974,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="10">
         <v>46210</v>
       </c>
@@ -2836,7 +2997,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="10">
         <v>46217</v>
       </c>
@@ -2859,7 +3020,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="10">
         <v>46224</v>
       </c>
@@ -2882,7 +3043,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="10">
         <v>46231</v>
       </c>
@@ -2905,7 +3066,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="10">
         <v>46238</v>
       </c>
@@ -2926,6 +3087,167 @@
       </c>
       <c r="G53" s="12">
         <v>109</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="B54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C54" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="12">
+        <v>106.5</v>
+      </c>
+      <c r="F54" s="12">
+        <v>110</v>
+      </c>
+      <c r="G54" s="12">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="B55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="C55" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="12">
+        <v>106.5</v>
+      </c>
+      <c r="F55" s="12">
+        <v>110</v>
+      </c>
+      <c r="G55" s="12">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="B56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="C56" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="12">
+        <v>104.5</v>
+      </c>
+      <c r="F56" s="12">
+        <v>108</v>
+      </c>
+      <c r="G56" s="12">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="B57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="C57" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="12">
+        <v>104.5</v>
+      </c>
+      <c r="F57" s="12">
+        <v>108</v>
+      </c>
+      <c r="G57" s="12">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="B58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="C58" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="12">
+        <v>104.5</v>
+      </c>
+      <c r="F58" s="12">
+        <v>108</v>
+      </c>
+      <c r="G58" s="12">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="B59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="C59" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="12">
+        <v>104.5</v>
+      </c>
+      <c r="F59" s="12">
+        <v>108</v>
+      </c>
+      <c r="G59" s="12">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="B60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="C60" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="12">
+        <v>104.5</v>
+      </c>
+      <c r="F60" s="12">
+        <v>108</v>
+      </c>
+      <c r="G60" s="12">
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -2936,19 +3258,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0C4456A-BBDC-4FAF-8248-C787C433008C}">
-  <dimension ref="A1:G53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G60"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="14"/>
-    <col min="7" max="7" width="11.19921875" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.1640625" style="14" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2971,7 +3293,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -2994,7 +3316,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -3017,7 +3339,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -3040,7 +3362,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -3063,7 +3385,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -3086,7 +3408,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -3109,7 +3431,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -3132,7 +3454,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -3155,7 +3477,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -3178,7 +3500,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -3201,7 +3523,7 @@
         <v>30.3</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -3224,7 +3546,7 @@
         <v>30.3</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -3247,7 +3569,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -3270,7 +3592,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -3293,7 +3615,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -3316,7 +3638,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -3339,7 +3661,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -3362,7 +3684,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -3385,7 +3707,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -3408,7 +3730,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -3431,7 +3753,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -3454,7 +3776,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -3477,7 +3799,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -3500,7 +3822,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -3523,7 +3845,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -3546,7 +3868,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -3569,7 +3891,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -3592,7 +3914,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -3615,7 +3937,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -3638,7 +3960,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -3661,7 +3983,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -3684,7 +4006,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -3707,7 +4029,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -3730,7 +4052,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -3753,7 +4075,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -3776,7 +4098,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -3799,7 +4121,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -3822,7 +4144,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -3845,7 +4167,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -3868,7 +4190,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -3891,7 +4213,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -3914,7 +4236,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -3937,7 +4259,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -3960,7 +4282,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -3983,7 +4305,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -4006,7 +4328,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -4029,7 +4351,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -4052,7 +4374,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="10">
         <v>46210</v>
       </c>
@@ -4075,7 +4397,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="10">
         <v>46217</v>
       </c>
@@ -4098,7 +4420,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="10">
         <v>46224</v>
       </c>
@@ -4121,7 +4443,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="10">
         <v>46231</v>
       </c>
@@ -4144,7 +4466,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="10">
         <v>46238</v>
       </c>
@@ -4165,6 +4487,167 @@
       </c>
       <c r="G53" s="14">
         <v>134</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="B54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C54" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="14">
+        <v>131</v>
+      </c>
+      <c r="F54" s="14">
+        <v>137</v>
+      </c>
+      <c r="G54" s="14">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="B55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="C55" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="14">
+        <v>131</v>
+      </c>
+      <c r="F55" s="14">
+        <v>137</v>
+      </c>
+      <c r="G55" s="14">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="B56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="C56" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="14">
+        <v>126</v>
+      </c>
+      <c r="F56" s="14">
+        <v>132</v>
+      </c>
+      <c r="G56" s="14">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="B57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="C57" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="14">
+        <v>126</v>
+      </c>
+      <c r="F57" s="14">
+        <v>132</v>
+      </c>
+      <c r="G57" s="14">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="B58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="C58" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="14">
+        <v>126</v>
+      </c>
+      <c r="F58" s="14">
+        <v>132</v>
+      </c>
+      <c r="G58" s="14">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="B59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="C59" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="14">
+        <v>126</v>
+      </c>
+      <c r="F59" s="14">
+        <v>132</v>
+      </c>
+      <c r="G59" s="14">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="B60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="C60" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="14">
+        <v>126</v>
+      </c>
+      <c r="F60" s="14">
+        <v>132</v>
+      </c>
+      <c r="G60" s="14">
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -4175,21 +4658,21 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CFD6F9F-3CCA-4363-AD1B-10496D95E8DB}">
-  <dimension ref="A1:H53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H60"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="14"/>
-    <col min="6" max="6" width="9.59765625" style="14" customWidth="1"/>
-    <col min="7" max="7" width="11.19921875" style="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.6640625" style="14" customWidth="1"/>
+    <col min="7" max="7" width="11.1640625" style="14" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9" style="15"/>
     <col min="9" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4212,7 +4695,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -4235,7 +4718,7 @@
         <v>33.5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -4258,7 +4741,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -4281,7 +4764,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -4304,7 +4787,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -4327,7 +4810,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -4350,7 +4833,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -4373,7 +4856,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -4396,7 +4879,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -4419,7 +4902,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -4442,7 +4925,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -4465,7 +4948,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -4488,7 +4971,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -4511,7 +4994,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -4534,7 +5017,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -4557,7 +5040,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -4580,7 +5063,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -4603,7 +5086,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -4626,7 +5109,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -4649,7 +5132,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -4672,7 +5155,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -4695,7 +5178,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -4718,7 +5201,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -4741,7 +5224,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -4764,7 +5247,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -4787,7 +5270,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -4810,7 +5293,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -4833,7 +5316,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -4856,7 +5339,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -4879,7 +5362,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -4902,7 +5385,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -4925,7 +5408,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -4948,7 +5431,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -4971,7 +5454,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -4994,7 +5477,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -5017,7 +5500,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -5040,7 +5523,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -5063,7 +5546,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -5086,7 +5569,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -5109,7 +5592,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -5132,7 +5615,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -5155,7 +5638,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -5178,7 +5661,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -5201,7 +5684,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -5224,7 +5707,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -5247,7 +5730,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -5270,7 +5753,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -5293,7 +5776,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="10">
         <v>46210</v>
       </c>
@@ -5316,7 +5799,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="10">
         <v>46217</v>
       </c>
@@ -5339,7 +5822,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="10">
         <v>46224</v>
       </c>
@@ -5362,7 +5845,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="10">
         <v>46231</v>
       </c>
@@ -5385,7 +5868,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="10">
         <v>46238</v>
       </c>
@@ -5406,6 +5889,167 @@
       </c>
       <c r="G53" s="14">
         <v>161</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="B54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C54" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="14">
+        <v>160</v>
+      </c>
+      <c r="F54" s="14">
+        <v>163.5</v>
+      </c>
+      <c r="G54" s="14">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="B55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="C55" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="14">
+        <v>160</v>
+      </c>
+      <c r="F55" s="14">
+        <v>163.5</v>
+      </c>
+      <c r="G55" s="14">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="B56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="C56" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="14">
+        <v>155</v>
+      </c>
+      <c r="F56" s="14">
+        <v>158.5</v>
+      </c>
+      <c r="G56" s="14">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="B57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="C57" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="14">
+        <v>155</v>
+      </c>
+      <c r="F57" s="14">
+        <v>158.5</v>
+      </c>
+      <c r="G57" s="14">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="B58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="C58" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="14">
+        <v>155</v>
+      </c>
+      <c r="F58" s="14">
+        <v>158.5</v>
+      </c>
+      <c r="G58" s="14">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="B59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="C59" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="14">
+        <v>155</v>
+      </c>
+      <c r="F59" s="14">
+        <v>158.5</v>
+      </c>
+      <c r="G59" s="14">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="B60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="C60" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="14">
+        <v>155</v>
+      </c>
+      <c r="F60" s="14">
+        <v>158.5</v>
+      </c>
+      <c r="G60" s="14">
+        <v>156</v>
       </c>
     </row>
   </sheetData>
